--- a/uploads/excel_format/bulk upload format.xlsx
+++ b/uploads/excel_format/bulk upload format.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="147">
   <si>
     <t>Sl.no</t>
   </si>
@@ -36,9 +36,6 @@
     <t>Cust Exist type</t>
   </si>
   <si>
-    <t>cus_name</t>
-  </si>
-  <si>
     <t>dob</t>
   </si>
   <si>
@@ -60,9 +57,6 @@
     <t>area</t>
   </si>
   <si>
-    <t>sub_area</t>
-  </si>
-  <si>
     <t>address</t>
   </si>
   <si>
@@ -81,9 +75,6 @@
     <t>spouse_name</t>
   </si>
   <si>
-    <t xml:space="preserve">Gurantor name </t>
-  </si>
-  <si>
     <t>guarantor relation ship</t>
   </si>
   <si>
@@ -105,9 +96,6 @@
     <t>loan_category</t>
   </si>
   <si>
-    <t>sub_category</t>
-  </si>
-  <si>
     <t>tot_value</t>
   </si>
   <si>
@@ -336,9 +324,6 @@
     <t>Appliance</t>
   </si>
   <si>
-    <t>Electronics</t>
-  </si>
-  <si>
     <t>Due Amount</t>
   </si>
   <si>
@@ -414,9 +399,6 @@
     <t>No.265, Ramalingasamy Street</t>
   </si>
   <si>
-    <t>P Ramarajan</t>
-  </si>
-  <si>
     <t>Closed Status</t>
   </si>
   <si>
@@ -457,6 +439,27 @@
   </si>
   <si>
     <t>xxx</t>
+  </si>
+  <si>
+    <t>first_name</t>
+  </si>
+  <si>
+    <t>last name</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gurantor first name </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ramarajan</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gurantor last name </t>
   </si>
 </sst>
 </file>
@@ -464,7 +467,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="[$-14009]yyyy/mm/dd;@"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -519,12 +522,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -537,6 +537,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -809,7 +814,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -821,34 +826,34 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" style="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" customWidth="1"/>
+    <col min="8" max="8" width="10.42578125" style="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14" customWidth="1"/>
     <col min="15" max="15" width="28.7109375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="11" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="17" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="20.42578125" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" customWidth="1"/>
+    <col min="23" max="23" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="17" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="7.5703125" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="9.28515625" bestFit="1" customWidth="1"/>
@@ -880,7 +885,7 @@
     <col min="59" max="59" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="60" max="60" width="21" bestFit="1" customWidth="1"/>
     <col min="61" max="62" width="21" customWidth="1"/>
-    <col min="63" max="63" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="10.42578125" style="12" bestFit="1" customWidth="1"/>
     <col min="64" max="64" width="11" bestFit="1" customWidth="1"/>
     <col min="65" max="65" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="66" max="66" width="9.42578125" bestFit="1" customWidth="1"/>
@@ -898,8 +903,8 @@
     <col min="78" max="78" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="79" max="79" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="80" max="81" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="82" max="82" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="83" max="83" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="82" max="82" width="14.85546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="15.5703125" style="12" bestFit="1" customWidth="1"/>
     <col min="84" max="84" width="18" bestFit="1" customWidth="1"/>
     <col min="85" max="85" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="86" max="86" width="18.85546875" bestFit="1" customWidth="1"/>
@@ -914,393 +919,393 @@
     <col min="95" max="95" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="96" max="96" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="97" max="98" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="99" max="99" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="99" max="99" width="11.5703125" style="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:99" s="9" customFormat="1">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:99" s="8" customFormat="1">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="I1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="J1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="K1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="L1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="M1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="N1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="O1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="P1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="Q1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="R1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="S1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="9" t="s">
+      <c r="T1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="9" t="s">
+      <c r="U1" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="V1" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="W1" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="9" t="s">
+      <c r="X1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="9" t="s">
+      <c r="Y1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="9" t="s">
+      <c r="Z1" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="9" t="s">
+      <c r="AA1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="9" t="s">
+      <c r="AB1" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="9" t="s">
+      <c r="AC1" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="9" t="s">
+      <c r="AD1" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="9" t="s">
+      <c r="AE1" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="9" t="s">
+      <c r="AF1" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="9" t="s">
+      <c r="AG1" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="9" t="s">
+      <c r="AH1" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="9" t="s">
+      <c r="AI1" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="9" t="s">
+      <c r="AJ1" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="9" t="s">
+      <c r="AK1" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="9" t="s">
+      <c r="AL1" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="9" t="s">
+      <c r="AM1" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="9" t="s">
+      <c r="AN1" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="9" t="s">
+      <c r="AO1" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="9" t="s">
+      <c r="AP1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="9" t="s">
+      <c r="AQ1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="9" t="s">
+      <c r="AR1" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="9" t="s">
+      <c r="AS1" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="9" t="s">
+      <c r="AT1" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="9" t="s">
+      <c r="AU1" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="9" t="s">
+      <c r="AV1" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="9" t="s">
+      <c r="AW1" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="9" t="s">
+      <c r="AX1" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="9" t="s">
+      <c r="AY1" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="9" t="s">
+      <c r="AZ1" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="9" t="s">
+      <c r="BA1" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="9" t="s">
+      <c r="BB1" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="9" t="s">
+      <c r="BC1" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="9" t="s">
+      <c r="BD1" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="9" t="s">
+      <c r="BE1" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" s="9" t="s">
+      <c r="BF1" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" s="9" t="s">
+      <c r="BG1" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" s="9" t="s">
+      <c r="BH1" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="9" t="s">
+      <c r="BI1" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="BJ1" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="BK1" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" s="9" t="s">
+      <c r="BL1" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" s="9" t="s">
+      <c r="BM1" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" s="9" t="s">
+      <c r="BN1" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="BJ1" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="BK1" s="9" t="s">
+      <c r="BO1" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="BL1" s="9" t="s">
+      <c r="BP1" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="BM1" s="9" t="s">
+      <c r="BQ1" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="BN1" s="9" t="s">
+      <c r="BR1" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="BO1" s="9" t="s">
+      <c r="BS1" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="BT1" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="BP1" s="9" t="s">
+      <c r="BU1" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="BQ1" s="9" t="s">
+      <c r="BV1" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="BR1" s="9" t="s">
+      <c r="BW1" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="BS1" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="BT1" s="9" t="s">
+      <c r="BX1" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="BU1" s="9" t="s">
+      <c r="BY1" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="BV1" s="9" t="s">
+      <c r="BZ1" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="BW1" s="9" t="s">
+      <c r="CA1" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="BX1" s="9" t="s">
+      <c r="CB1" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="BY1" s="9" t="s">
+      <c r="CC1" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="BZ1" s="9" t="s">
+      <c r="CD1" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="CA1" s="9" t="s">
+      <c r="CE1" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="CB1" s="9" t="s">
+      <c r="CF1" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="CC1" s="9" t="s">
+      <c r="CG1" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="CD1" s="9" t="s">
+      <c r="CH1" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="CE1" s="9" t="s">
+      <c r="CI1" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="CF1" s="9" t="s">
+      <c r="CJ1" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="CG1" s="9" t="s">
+      <c r="CK1" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="CH1" s="9" t="s">
+      <c r="CL1" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="CI1" s="9" t="s">
+      <c r="CM1" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="CJ1" s="9" t="s">
+      <c r="CN1" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="CK1" s="9" t="s">
+      <c r="CO1" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="CL1" s="9" t="s">
+      <c r="CP1" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="CM1" s="9" t="s">
+      <c r="CQ1" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="CN1" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="CO1" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="CP1" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="CQ1" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="CR1" s="9" t="s">
+      <c r="CR1" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="CS1" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="CT1" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="CU1" s="10" t="s">
         <v>132</v>
-      </c>
-      <c r="CS1" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="CT1" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="CU1" s="9" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:99" ht="15.75">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="11">
         <v>45238</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="2">
         <v>271232712327</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="H2" s="11">
+        <v>32874</v>
+      </c>
+      <c r="I2" s="3">
+        <v>34</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="G2" s="2">
-        <v>32874</v>
-      </c>
-      <c r="H2" s="4">
-        <v>34</v>
-      </c>
-      <c r="I2" s="1" t="s">
+      <c r="N2" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>130</v>
+      <c r="O2" s="4" t="s">
+        <v>125</v>
       </c>
       <c r="P2" s="1">
         <v>2712327123</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="Q2" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="W2" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="R2" s="5" t="s">
+      <c r="X2" s="2">
+        <v>111111111111</v>
+      </c>
+      <c r="Y2" s="3">
+        <v>30</v>
+      </c>
+      <c r="Z2" s="1">
+        <v>8124222132</v>
+      </c>
+      <c r="AA2" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="AB2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="T2" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="U2" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="W2" s="3">
-        <v>111111111111</v>
-      </c>
-      <c r="X2" s="4">
-        <v>30</v>
-      </c>
-      <c r="Y2" s="1">
-        <v>8124222132</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="AA2" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC2" s="6" t="s">
-        <v>105</v>
       </c>
       <c r="AD2" s="1">
         <v>15000</v>
@@ -1312,21 +1317,21 @@
         <v>15000</v>
       </c>
       <c r="AG2" s="1" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="AH2" s="1">
         <v>2800</v>
       </c>
-      <c r="AI2" s="4"/>
-      <c r="AJ2" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="AK2" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="AL2" s="4"/>
+      <c r="AI2" s="3"/>
+      <c r="AJ2" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="AK2" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="AL2" s="3"/>
       <c r="AM2" s="1" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="AN2" s="1">
         <v>0</v>
@@ -1356,71 +1361,71 @@
         <v>100000</v>
       </c>
       <c r="AW2" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AX2" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AY2" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="AZ2" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="BA2" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="BB2" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="BC2" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="AX2" s="1" t="s">
+      <c r="BD2" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="AY2" s="1" t="s">
+      <c r="BE2" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="BF2" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG2" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="AZ2" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="BA2" s="1" t="s">
+      <c r="BH2" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="BI2" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="BJ2" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="BK2" s="11">
+        <v>45238</v>
+      </c>
+      <c r="BL2" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="BB2" s="1" t="s">
+      <c r="BM2" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="BC2" s="5" t="s">
+      <c r="BN2" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="BD2" s="1" t="s">
+      <c r="BO2" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="BE2" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="BF2" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="BG2" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="BH2" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="BI2" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="BJ2" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="BK2" s="2">
-        <v>45238</v>
-      </c>
-      <c r="BL2" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="BM2" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="BN2" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="BO2" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="BP2" s="4"/>
-      <c r="BQ2" s="4"/>
+      <c r="BP2" s="3"/>
+      <c r="BQ2" s="3"/>
       <c r="BR2" s="1">
         <v>2</v>
       </c>
       <c r="BS2" s="1">
         <v>6</v>
       </c>
-      <c r="BT2" s="4">
+      <c r="BT2" s="3">
         <v>2</v>
       </c>
       <c r="BU2" s="1">
@@ -1432,118 +1437,118 @@
       <c r="BW2" s="1">
         <v>15000</v>
       </c>
-      <c r="BX2" s="7">
+      <c r="BX2" s="6">
         <v>1800</v>
       </c>
-      <c r="BY2" s="7">
+      <c r="BY2" s="6">
         <v>16800</v>
       </c>
       <c r="BZ2" s="1">
         <v>2800</v>
       </c>
-      <c r="CA2" s="7">
+      <c r="CA2" s="6">
         <v>300</v>
       </c>
-      <c r="CB2" s="4">
+      <c r="CB2" s="3">
         <v>0</v>
       </c>
-      <c r="CC2" s="7">
+      <c r="CC2" s="6">
         <v>14700</v>
       </c>
-      <c r="CD2" s="2">
+      <c r="CD2" s="11">
         <v>45270</v>
       </c>
-      <c r="CE2" s="2">
+      <c r="CE2" s="11">
         <v>45422</v>
       </c>
       <c r="CF2" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="CG2" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="CH2" s="2">
+        <v>239903777436</v>
+      </c>
+      <c r="CI2" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="CJ2" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="CK2" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="CL2" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="CM2" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="CG2" s="1" t="s">
+      <c r="CN2" s="6">
+        <v>14700</v>
+      </c>
+      <c r="CO2" s="3">
+        <v>0</v>
+      </c>
+      <c r="CP2" s="2">
+        <v>239903777436</v>
+      </c>
+      <c r="CQ2" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="CH2" s="3">
-        <v>239903777436</v>
-      </c>
-      <c r="CI2" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="CJ2" s="5" t="s">
+      <c r="CR2" t="s">
         <v>129</v>
       </c>
-      <c r="CK2" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="CL2" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="CM2" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="CN2" s="7">
-        <v>14700</v>
-      </c>
-      <c r="CO2" s="4">
-        <v>0</v>
-      </c>
-      <c r="CP2" s="3">
-        <v>239903777436</v>
-      </c>
-      <c r="CQ2" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="CR2" t="s">
-        <v>135</v>
-      </c>
       <c r="CS2" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="CT2" t="s">
-        <v>137</v>
-      </c>
-      <c r="CU2" s="2">
+        <v>131</v>
+      </c>
+      <c r="CU2" s="11">
         <v>45483</v>
       </c>
     </row>
     <row r="3" spans="1:99">
       <c r="A3" s="1"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="3"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="2"/>
       <c r="D3" s="1"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="1"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="3"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="8"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="7"/>
       <c r="P3" s="1"/>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="5"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="4"/>
       <c r="S3" s="1"/>
-      <c r="T3" s="8"/>
-      <c r="U3" s="8"/>
-      <c r="V3" s="1"/>
-      <c r="W3" s="3"/>
-      <c r="X3" s="4"/>
-      <c r="Y3" s="1"/>
+      <c r="T3" s="7"/>
+      <c r="U3" s="7"/>
+      <c r="V3" s="7"/>
+      <c r="W3" s="1"/>
+      <c r="X3" s="2"/>
+      <c r="Y3" s="3"/>
       <c r="Z3" s="1"/>
       <c r="AA3" s="1"/>
-      <c r="AB3" s="6"/>
-      <c r="AC3" s="6"/>
+      <c r="AB3" s="1"/>
+      <c r="AC3" s="5"/>
       <c r="AD3" s="1"/>
       <c r="AE3" s="1"/>
       <c r="AF3" s="1"/>
       <c r="AG3" s="1"/>
       <c r="AH3" s="1"/>
-      <c r="AI3" s="4"/>
-      <c r="AJ3" s="8"/>
-      <c r="AK3" s="8"/>
-      <c r="AL3" s="4"/>
+      <c r="AI3" s="3"/>
+      <c r="AJ3" s="7"/>
+      <c r="AK3" s="7"/>
+      <c r="AL3" s="3"/>
       <c r="AM3" s="1"/>
       <c r="AN3" s="1"/>
       <c r="AO3" s="1"/>
@@ -1557,85 +1562,85 @@
       <c r="AW3" s="1"/>
       <c r="AX3" s="1"/>
       <c r="AY3" s="1"/>
-      <c r="AZ3" s="8"/>
+      <c r="AZ3" s="7"/>
       <c r="BA3" s="1"/>
       <c r="BB3" s="1"/>
-      <c r="BC3" s="8"/>
+      <c r="BC3" s="7"/>
       <c r="BD3" s="1"/>
-      <c r="BE3" s="4"/>
-      <c r="BF3" s="4"/>
+      <c r="BE3" s="3"/>
+      <c r="BF3" s="3"/>
       <c r="BG3" s="1"/>
       <c r="BH3" s="1"/>
       <c r="BI3" s="1"/>
       <c r="BJ3" s="1"/>
-      <c r="BK3" s="2"/>
+      <c r="BK3" s="11"/>
       <c r="BL3" s="1"/>
       <c r="BM3" s="1"/>
       <c r="BN3" s="1"/>
       <c r="BO3" s="1"/>
-      <c r="BP3" s="4"/>
-      <c r="BQ3" s="4"/>
+      <c r="BP3" s="3"/>
+      <c r="BQ3" s="3"/>
       <c r="BR3" s="1"/>
       <c r="BS3" s="1"/>
-      <c r="BT3" s="4"/>
+      <c r="BT3" s="3"/>
       <c r="BU3" s="1"/>
       <c r="BV3" s="1"/>
       <c r="BW3" s="1"/>
       <c r="BZ3" s="1"/>
-      <c r="CB3" s="4"/>
-      <c r="CD3" s="2"/>
-      <c r="CE3" s="2"/>
+      <c r="CB3" s="3"/>
+      <c r="CD3" s="11"/>
+      <c r="CE3" s="11"/>
       <c r="CF3" s="1"/>
       <c r="CG3" s="1"/>
-      <c r="CH3" s="3"/>
+      <c r="CH3" s="2"/>
       <c r="CI3" s="1"/>
-      <c r="CJ3" s="8"/>
-      <c r="CK3" s="6"/>
+      <c r="CJ3" s="7"/>
+      <c r="CK3" s="5"/>
       <c r="CL3" s="1"/>
       <c r="CM3" s="1"/>
-      <c r="CO3" s="4"/>
-      <c r="CP3" s="3"/>
+      <c r="CO3" s="3"/>
+      <c r="CP3" s="2"/>
       <c r="CQ3" s="1"/>
     </row>
     <row r="4" spans="1:99">
       <c r="A4" s="1"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="3"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="2"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="1"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="3"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="8"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="7"/>
       <c r="P4" s="1"/>
-      <c r="Q4" s="8"/>
-      <c r="R4" s="5"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="4"/>
       <c r="S4" s="1"/>
-      <c r="T4" s="8"/>
-      <c r="U4" s="8"/>
-      <c r="V4" s="1"/>
-      <c r="W4" s="3"/>
-      <c r="X4" s="4"/>
-      <c r="Y4" s="1"/>
+      <c r="T4" s="7"/>
+      <c r="U4" s="7"/>
+      <c r="V4" s="7"/>
+      <c r="W4" s="1"/>
+      <c r="X4" s="2"/>
+      <c r="Y4" s="3"/>
       <c r="Z4" s="1"/>
       <c r="AA4" s="1"/>
-      <c r="AB4" s="6"/>
-      <c r="AC4" s="6"/>
+      <c r="AB4" s="1"/>
+      <c r="AC4" s="5"/>
       <c r="AD4" s="1"/>
       <c r="AE4" s="1"/>
       <c r="AF4" s="1"/>
       <c r="AG4" s="1"/>
       <c r="AH4" s="1"/>
-      <c r="AI4" s="4"/>
-      <c r="AJ4" s="8"/>
-      <c r="AK4" s="8"/>
-      <c r="AL4" s="4"/>
+      <c r="AI4" s="3"/>
+      <c r="AJ4" s="7"/>
+      <c r="AK4" s="7"/>
+      <c r="AL4" s="3"/>
       <c r="AM4" s="1"/>
       <c r="AN4" s="1"/>
       <c r="AO4" s="1"/>
@@ -1649,85 +1654,85 @@
       <c r="AW4" s="1"/>
       <c r="AX4" s="1"/>
       <c r="AY4" s="1"/>
-      <c r="AZ4" s="8"/>
+      <c r="AZ4" s="7"/>
       <c r="BA4" s="1"/>
       <c r="BB4" s="1"/>
-      <c r="BC4" s="8"/>
+      <c r="BC4" s="7"/>
       <c r="BD4" s="1"/>
-      <c r="BE4" s="4"/>
-      <c r="BF4" s="4"/>
+      <c r="BE4" s="3"/>
+      <c r="BF4" s="3"/>
       <c r="BG4" s="1"/>
       <c r="BH4" s="1"/>
       <c r="BI4" s="1"/>
       <c r="BJ4" s="1"/>
-      <c r="BK4" s="2"/>
+      <c r="BK4" s="11"/>
       <c r="BL4" s="1"/>
       <c r="BM4" s="1"/>
       <c r="BN4" s="1"/>
       <c r="BO4" s="1"/>
-      <c r="BP4" s="4"/>
-      <c r="BQ4" s="4"/>
+      <c r="BP4" s="3"/>
+      <c r="BQ4" s="3"/>
       <c r="BR4" s="1"/>
       <c r="BS4" s="1"/>
-      <c r="BT4" s="4"/>
+      <c r="BT4" s="3"/>
       <c r="BU4" s="1"/>
       <c r="BV4" s="1"/>
       <c r="BW4" s="1"/>
       <c r="BZ4" s="1"/>
-      <c r="CB4" s="4"/>
-      <c r="CD4" s="2"/>
-      <c r="CE4" s="2"/>
+      <c r="CB4" s="3"/>
+      <c r="CD4" s="11"/>
+      <c r="CE4" s="11"/>
       <c r="CF4" s="1"/>
       <c r="CG4" s="1"/>
-      <c r="CH4" s="3"/>
+      <c r="CH4" s="2"/>
       <c r="CI4" s="1"/>
-      <c r="CJ4" s="8"/>
-      <c r="CK4" s="6"/>
+      <c r="CJ4" s="7"/>
+      <c r="CK4" s="5"/>
       <c r="CL4" s="1"/>
       <c r="CM4" s="1"/>
-      <c r="CO4" s="4"/>
-      <c r="CP4" s="3"/>
+      <c r="CO4" s="3"/>
+      <c r="CP4" s="2"/>
       <c r="CQ4" s="1"/>
     </row>
     <row r="5" spans="1:99">
       <c r="A5" s="1"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="3"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="2"/>
       <c r="D5" s="1"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="1"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="3"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="8"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="7"/>
       <c r="P5" s="1"/>
-      <c r="Q5" s="8"/>
-      <c r="R5" s="5"/>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="4"/>
       <c r="S5" s="1"/>
-      <c r="T5" s="8"/>
-      <c r="U5" s="8"/>
-      <c r="V5" s="1"/>
-      <c r="W5" s="3"/>
-      <c r="X5" s="4"/>
-      <c r="Y5" s="1"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7"/>
+      <c r="V5" s="7"/>
+      <c r="W5" s="1"/>
+      <c r="X5" s="2"/>
+      <c r="Y5" s="3"/>
       <c r="Z5" s="1"/>
       <c r="AA5" s="1"/>
-      <c r="AB5" s="6"/>
-      <c r="AC5" s="6"/>
+      <c r="AB5" s="1"/>
+      <c r="AC5" s="5"/>
       <c r="AD5" s="1"/>
       <c r="AE5" s="1"/>
       <c r="AF5" s="1"/>
       <c r="AG5" s="1"/>
       <c r="AH5" s="1"/>
-      <c r="AI5" s="4"/>
-      <c r="AJ5" s="8"/>
-      <c r="AK5" s="8"/>
-      <c r="AL5" s="4"/>
+      <c r="AI5" s="3"/>
+      <c r="AJ5" s="7"/>
+      <c r="AK5" s="7"/>
+      <c r="AL5" s="3"/>
       <c r="AM5" s="1"/>
       <c r="AN5" s="1"/>
       <c r="AO5" s="1"/>
@@ -1741,85 +1746,85 @@
       <c r="AW5" s="1"/>
       <c r="AX5" s="1"/>
       <c r="AY5" s="1"/>
-      <c r="AZ5" s="8"/>
+      <c r="AZ5" s="7"/>
       <c r="BA5" s="1"/>
       <c r="BB5" s="1"/>
-      <c r="BC5" s="8"/>
+      <c r="BC5" s="7"/>
       <c r="BD5" s="1"/>
-      <c r="BE5" s="4"/>
-      <c r="BF5" s="4"/>
+      <c r="BE5" s="3"/>
+      <c r="BF5" s="3"/>
       <c r="BG5" s="1"/>
       <c r="BH5" s="1"/>
       <c r="BI5" s="1"/>
       <c r="BJ5" s="1"/>
-      <c r="BK5" s="2"/>
+      <c r="BK5" s="11"/>
       <c r="BL5" s="1"/>
       <c r="BM5" s="1"/>
       <c r="BN5" s="1"/>
       <c r="BO5" s="1"/>
-      <c r="BP5" s="4"/>
-      <c r="BQ5" s="4"/>
+      <c r="BP5" s="3"/>
+      <c r="BQ5" s="3"/>
       <c r="BR5" s="1"/>
       <c r="BS5" s="1"/>
-      <c r="BT5" s="4"/>
+      <c r="BT5" s="3"/>
       <c r="BU5" s="1"/>
       <c r="BV5" s="1"/>
       <c r="BW5" s="1"/>
       <c r="BZ5" s="1"/>
-      <c r="CB5" s="4"/>
-      <c r="CD5" s="2"/>
-      <c r="CE5" s="2"/>
+      <c r="CB5" s="3"/>
+      <c r="CD5" s="11"/>
+      <c r="CE5" s="11"/>
       <c r="CF5" s="1"/>
       <c r="CG5" s="1"/>
-      <c r="CH5" s="3"/>
+      <c r="CH5" s="2"/>
       <c r="CI5" s="1"/>
-      <c r="CJ5" s="8"/>
-      <c r="CK5" s="6"/>
+      <c r="CJ5" s="7"/>
+      <c r="CK5" s="5"/>
       <c r="CL5" s="1"/>
       <c r="CM5" s="1"/>
-      <c r="CO5" s="4"/>
-      <c r="CP5" s="3"/>
+      <c r="CO5" s="3"/>
+      <c r="CP5" s="2"/>
       <c r="CQ5" s="1"/>
     </row>
     <row r="6" spans="1:99">
       <c r="A6" s="1"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="3"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="2"/>
       <c r="D6" s="1"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="1"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="3"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="8"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="7"/>
       <c r="P6" s="1"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="5"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="4"/>
       <c r="S6" s="1"/>
-      <c r="T6" s="8"/>
-      <c r="U6" s="8"/>
-      <c r="V6" s="1"/>
-      <c r="W6" s="3"/>
-      <c r="X6" s="4"/>
-      <c r="Y6" s="1"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7"/>
+      <c r="V6" s="7"/>
+      <c r="W6" s="1"/>
+      <c r="X6" s="2"/>
+      <c r="Y6" s="3"/>
       <c r="Z6" s="1"/>
       <c r="AA6" s="1"/>
-      <c r="AB6" s="6"/>
-      <c r="AC6" s="4"/>
+      <c r="AB6" s="1"/>
+      <c r="AC6" s="5"/>
       <c r="AD6" s="1"/>
       <c r="AE6" s="1"/>
       <c r="AF6" s="1"/>
       <c r="AG6" s="1"/>
       <c r="AH6" s="1"/>
-      <c r="AI6" s="4"/>
-      <c r="AJ6" s="8"/>
-      <c r="AK6" s="8"/>
-      <c r="AL6" s="4"/>
+      <c r="AI6" s="3"/>
+      <c r="AJ6" s="7"/>
+      <c r="AK6" s="7"/>
+      <c r="AL6" s="3"/>
       <c r="AM6" s="1"/>
       <c r="AN6" s="1"/>
       <c r="AO6" s="1"/>
@@ -1833,84 +1838,84 @@
       <c r="AW6" s="1"/>
       <c r="AX6" s="1"/>
       <c r="AY6" s="1"/>
-      <c r="AZ6" s="8"/>
+      <c r="AZ6" s="7"/>
       <c r="BA6" s="1"/>
       <c r="BB6" s="1"/>
-      <c r="BC6" s="8"/>
+      <c r="BC6" s="7"/>
       <c r="BD6" s="1"/>
-      <c r="BE6" s="4"/>
-      <c r="BF6" s="4"/>
+      <c r="BE6" s="3"/>
+      <c r="BF6" s="3"/>
       <c r="BG6" s="1"/>
       <c r="BH6" s="1"/>
       <c r="BI6" s="1"/>
       <c r="BJ6" s="1"/>
-      <c r="BK6" s="2"/>
+      <c r="BK6" s="11"/>
       <c r="BL6" s="1"/>
       <c r="BM6" s="1"/>
       <c r="BN6" s="1"/>
       <c r="BO6" s="1"/>
-      <c r="BP6" s="4"/>
-      <c r="BQ6" s="4"/>
+      <c r="BP6" s="3"/>
+      <c r="BQ6" s="3"/>
       <c r="BR6" s="1"/>
       <c r="BS6" s="1"/>
       <c r="BU6" s="1"/>
       <c r="BV6" s="1"/>
       <c r="BW6" s="1"/>
       <c r="BZ6" s="1"/>
-      <c r="CB6" s="4"/>
-      <c r="CD6" s="2"/>
-      <c r="CE6" s="2"/>
+      <c r="CB6" s="3"/>
+      <c r="CD6" s="11"/>
+      <c r="CE6" s="11"/>
       <c r="CF6" s="1"/>
       <c r="CG6" s="1"/>
-      <c r="CH6" s="3"/>
+      <c r="CH6" s="2"/>
       <c r="CI6" s="1"/>
-      <c r="CJ6" s="8"/>
-      <c r="CK6" s="6"/>
+      <c r="CJ6" s="7"/>
+      <c r="CK6" s="5"/>
       <c r="CL6" s="1"/>
       <c r="CM6" s="1"/>
-      <c r="CO6" s="4"/>
-      <c r="CP6" s="3"/>
+      <c r="CO6" s="3"/>
+      <c r="CP6" s="2"/>
       <c r="CQ6" s="1"/>
     </row>
     <row r="7" spans="1:99">
       <c r="A7" s="1"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="3"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="2"/>
       <c r="D7" s="1"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="1"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="3"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="8"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="7"/>
       <c r="P7" s="1"/>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="5"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="4"/>
       <c r="S7" s="1"/>
-      <c r="T7" s="8"/>
-      <c r="U7" s="8"/>
-      <c r="V7" s="1"/>
-      <c r="W7" s="3"/>
-      <c r="X7" s="4"/>
-      <c r="Y7" s="1"/>
+      <c r="T7" s="7"/>
+      <c r="U7" s="7"/>
+      <c r="V7" s="7"/>
+      <c r="W7" s="1"/>
+      <c r="X7" s="2"/>
+      <c r="Y7" s="3"/>
       <c r="Z7" s="1"/>
       <c r="AA7" s="1"/>
-      <c r="AB7" s="6"/>
-      <c r="AC7" s="4"/>
+      <c r="AB7" s="1"/>
+      <c r="AC7" s="5"/>
       <c r="AD7" s="1"/>
       <c r="AE7" s="1"/>
       <c r="AF7" s="1"/>
       <c r="AG7" s="1"/>
       <c r="AH7" s="1"/>
-      <c r="AI7" s="4"/>
-      <c r="AJ7" s="8"/>
-      <c r="AK7" s="8"/>
-      <c r="AL7" s="4"/>
+      <c r="AI7" s="3"/>
+      <c r="AJ7" s="7"/>
+      <c r="AK7" s="7"/>
+      <c r="AL7" s="3"/>
       <c r="AM7" s="1"/>
       <c r="AN7" s="1"/>
       <c r="AO7" s="1"/>
@@ -1924,84 +1929,84 @@
       <c r="AW7" s="1"/>
       <c r="AX7" s="1"/>
       <c r="AY7" s="1"/>
-      <c r="AZ7" s="8"/>
+      <c r="AZ7" s="7"/>
       <c r="BA7" s="1"/>
       <c r="BB7" s="1"/>
-      <c r="BC7" s="8"/>
+      <c r="BC7" s="7"/>
       <c r="BD7" s="1"/>
-      <c r="BE7" s="4"/>
-      <c r="BF7" s="4"/>
+      <c r="BE7" s="3"/>
+      <c r="BF7" s="3"/>
       <c r="BG7" s="1"/>
       <c r="BH7" s="1"/>
       <c r="BI7" s="1"/>
       <c r="BJ7" s="1"/>
-      <c r="BK7" s="2"/>
+      <c r="BK7" s="11"/>
       <c r="BL7" s="1"/>
       <c r="BM7" s="1"/>
       <c r="BN7" s="1"/>
       <c r="BO7" s="1"/>
-      <c r="BP7" s="4"/>
-      <c r="BQ7" s="4"/>
+      <c r="BP7" s="3"/>
+      <c r="BQ7" s="3"/>
       <c r="BR7" s="1"/>
       <c r="BS7" s="1"/>
       <c r="BU7" s="1"/>
       <c r="BV7" s="1"/>
       <c r="BW7" s="1"/>
       <c r="BZ7" s="1"/>
-      <c r="CB7" s="4"/>
-      <c r="CD7" s="2"/>
-      <c r="CE7" s="2"/>
+      <c r="CB7" s="3"/>
+      <c r="CD7" s="11"/>
+      <c r="CE7" s="11"/>
       <c r="CF7" s="1"/>
       <c r="CG7" s="1"/>
-      <c r="CH7" s="3"/>
+      <c r="CH7" s="2"/>
       <c r="CI7" s="1"/>
-      <c r="CJ7" s="8"/>
-      <c r="CK7" s="6"/>
+      <c r="CJ7" s="7"/>
+      <c r="CK7" s="5"/>
       <c r="CL7" s="1"/>
       <c r="CM7" s="1"/>
-      <c r="CO7" s="4"/>
-      <c r="CP7" s="3"/>
+      <c r="CO7" s="3"/>
+      <c r="CP7" s="2"/>
       <c r="CQ7" s="1"/>
     </row>
     <row r="8" spans="1:99">
       <c r="A8" s="1"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="3"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="2"/>
       <c r="D8" s="1"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="1"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="3"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="8"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="7"/>
       <c r="P8" s="1"/>
-      <c r="Q8" s="8"/>
-      <c r="R8" s="5"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="4"/>
       <c r="S8" s="1"/>
-      <c r="T8" s="8"/>
-      <c r="U8" s="8"/>
-      <c r="V8" s="1"/>
-      <c r="W8" s="3"/>
-      <c r="X8" s="4"/>
-      <c r="Y8" s="1"/>
+      <c r="T8" s="7"/>
+      <c r="U8" s="7"/>
+      <c r="V8" s="7"/>
+      <c r="W8" s="1"/>
+      <c r="X8" s="2"/>
+      <c r="Y8" s="3"/>
       <c r="Z8" s="1"/>
       <c r="AA8" s="1"/>
-      <c r="AB8" s="6"/>
-      <c r="AC8" s="4"/>
+      <c r="AB8" s="1"/>
+      <c r="AC8" s="5"/>
       <c r="AD8" s="1"/>
       <c r="AE8" s="1"/>
       <c r="AF8" s="1"/>
       <c r="AG8" s="1"/>
       <c r="AH8" s="1"/>
-      <c r="AI8" s="4"/>
-      <c r="AJ8" s="8"/>
-      <c r="AK8" s="8"/>
-      <c r="AL8" s="4"/>
+      <c r="AI8" s="3"/>
+      <c r="AJ8" s="7"/>
+      <c r="AK8" s="7"/>
+      <c r="AL8" s="3"/>
       <c r="AM8" s="1"/>
       <c r="AN8" s="1"/>
       <c r="AO8" s="1"/>
@@ -2015,84 +2020,84 @@
       <c r="AW8" s="1"/>
       <c r="AX8" s="1"/>
       <c r="AY8" s="1"/>
-      <c r="AZ8" s="8"/>
+      <c r="AZ8" s="7"/>
       <c r="BA8" s="1"/>
       <c r="BB8" s="1"/>
-      <c r="BC8" s="8"/>
+      <c r="BC8" s="7"/>
       <c r="BD8" s="1"/>
-      <c r="BE8" s="4"/>
-      <c r="BF8" s="4"/>
+      <c r="BE8" s="3"/>
+      <c r="BF8" s="3"/>
       <c r="BG8" s="1"/>
       <c r="BH8" s="1"/>
       <c r="BI8" s="1"/>
       <c r="BJ8" s="1"/>
-      <c r="BK8" s="2"/>
+      <c r="BK8" s="11"/>
       <c r="BL8" s="1"/>
       <c r="BM8" s="1"/>
       <c r="BN8" s="1"/>
       <c r="BO8" s="1"/>
-      <c r="BP8" s="4"/>
-      <c r="BQ8" s="4"/>
+      <c r="BP8" s="3"/>
+      <c r="BQ8" s="3"/>
       <c r="BR8" s="1"/>
       <c r="BS8" s="1"/>
       <c r="BU8" s="1"/>
       <c r="BV8" s="1"/>
       <c r="BW8" s="1"/>
       <c r="BZ8" s="1"/>
-      <c r="CB8" s="4"/>
-      <c r="CD8" s="2"/>
-      <c r="CE8" s="2"/>
+      <c r="CB8" s="3"/>
+      <c r="CD8" s="11"/>
+      <c r="CE8" s="11"/>
       <c r="CF8" s="1"/>
       <c r="CG8" s="1"/>
-      <c r="CH8" s="3"/>
+      <c r="CH8" s="2"/>
       <c r="CI8" s="1"/>
-      <c r="CJ8" s="8"/>
-      <c r="CK8" s="6"/>
+      <c r="CJ8" s="7"/>
+      <c r="CK8" s="5"/>
       <c r="CL8" s="1"/>
       <c r="CM8" s="1"/>
-      <c r="CO8" s="4"/>
-      <c r="CP8" s="3"/>
+      <c r="CO8" s="3"/>
+      <c r="CP8" s="2"/>
       <c r="CQ8" s="1"/>
     </row>
     <row r="9" spans="1:99">
       <c r="A9" s="1"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="3"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="2"/>
       <c r="D9" s="1"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="1"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="3"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="8"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="7"/>
       <c r="P9" s="1"/>
-      <c r="Q9" s="8"/>
-      <c r="R9" s="5"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="4"/>
       <c r="S9" s="1"/>
-      <c r="T9" s="8"/>
-      <c r="U9" s="8"/>
-      <c r="V9" s="1"/>
-      <c r="W9" s="3"/>
-      <c r="X9" s="4"/>
-      <c r="Y9" s="1"/>
+      <c r="T9" s="7"/>
+      <c r="U9" s="7"/>
+      <c r="V9" s="7"/>
+      <c r="W9" s="1"/>
+      <c r="X9" s="2"/>
+      <c r="Y9" s="3"/>
       <c r="Z9" s="1"/>
       <c r="AA9" s="1"/>
-      <c r="AB9" s="6"/>
-      <c r="AC9" s="4"/>
+      <c r="AB9" s="1"/>
+      <c r="AC9" s="5"/>
       <c r="AD9" s="1"/>
       <c r="AE9" s="1"/>
       <c r="AF9" s="1"/>
       <c r="AG9" s="1"/>
       <c r="AH9" s="1"/>
-      <c r="AI9" s="4"/>
-      <c r="AJ9" s="8"/>
-      <c r="AK9" s="8"/>
-      <c r="AL9" s="4"/>
+      <c r="AI9" s="3"/>
+      <c r="AJ9" s="7"/>
+      <c r="AK9" s="7"/>
+      <c r="AL9" s="3"/>
       <c r="AM9" s="1"/>
       <c r="AN9" s="1"/>
       <c r="AO9" s="1"/>
@@ -2106,84 +2111,84 @@
       <c r="AW9" s="1"/>
       <c r="AX9" s="1"/>
       <c r="AY9" s="1"/>
-      <c r="AZ9" s="8"/>
+      <c r="AZ9" s="7"/>
       <c r="BA9" s="1"/>
       <c r="BB9" s="1"/>
-      <c r="BC9" s="8"/>
+      <c r="BC9" s="7"/>
       <c r="BD9" s="1"/>
-      <c r="BE9" s="4"/>
-      <c r="BF9" s="4"/>
+      <c r="BE9" s="3"/>
+      <c r="BF9" s="3"/>
       <c r="BG9" s="1"/>
       <c r="BH9" s="1"/>
       <c r="BI9" s="1"/>
       <c r="BJ9" s="1"/>
-      <c r="BK9" s="2"/>
+      <c r="BK9" s="11"/>
       <c r="BL9" s="1"/>
       <c r="BM9" s="1"/>
       <c r="BN9" s="1"/>
       <c r="BO9" s="1"/>
-      <c r="BP9" s="4"/>
-      <c r="BQ9" s="4"/>
+      <c r="BP9" s="3"/>
+      <c r="BQ9" s="3"/>
       <c r="BR9" s="1"/>
       <c r="BS9" s="1"/>
       <c r="BU9" s="1"/>
       <c r="BV9" s="1"/>
       <c r="BW9" s="1"/>
       <c r="BZ9" s="1"/>
-      <c r="CB9" s="4"/>
-      <c r="CD9" s="2"/>
-      <c r="CE9" s="2"/>
+      <c r="CB9" s="3"/>
+      <c r="CD9" s="11"/>
+      <c r="CE9" s="11"/>
       <c r="CF9" s="1"/>
       <c r="CG9" s="1"/>
-      <c r="CH9" s="3"/>
+      <c r="CH9" s="2"/>
       <c r="CI9" s="1"/>
-      <c r="CJ9" s="8"/>
-      <c r="CK9" s="6"/>
+      <c r="CJ9" s="7"/>
+      <c r="CK9" s="5"/>
       <c r="CL9" s="1"/>
       <c r="CM9" s="1"/>
-      <c r="CO9" s="4"/>
-      <c r="CP9" s="3"/>
+      <c r="CO9" s="3"/>
+      <c r="CP9" s="2"/>
       <c r="CQ9" s="1"/>
     </row>
     <row r="10" spans="1:99">
       <c r="A10" s="1"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="3"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="2"/>
       <c r="D10" s="1"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="1"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="3"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
-      <c r="O10" s="8"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="7"/>
       <c r="P10" s="1"/>
-      <c r="Q10" s="8"/>
-      <c r="R10" s="5"/>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="4"/>
       <c r="S10" s="1"/>
-      <c r="T10" s="8"/>
-      <c r="U10" s="8"/>
-      <c r="V10" s="1"/>
-      <c r="W10" s="3"/>
-      <c r="X10" s="4"/>
-      <c r="Y10" s="1"/>
+      <c r="T10" s="7"/>
+      <c r="U10" s="7"/>
+      <c r="V10" s="7"/>
+      <c r="W10" s="1"/>
+      <c r="X10" s="2"/>
+      <c r="Y10" s="3"/>
       <c r="Z10" s="1"/>
       <c r="AA10" s="1"/>
-      <c r="AB10" s="6"/>
-      <c r="AC10" s="6"/>
+      <c r="AB10" s="1"/>
+      <c r="AC10" s="5"/>
       <c r="AD10" s="1"/>
       <c r="AE10" s="1"/>
       <c r="AF10" s="1"/>
       <c r="AG10" s="1"/>
       <c r="AH10" s="1"/>
-      <c r="AI10" s="4"/>
-      <c r="AJ10" s="8"/>
-      <c r="AK10" s="8"/>
-      <c r="AL10" s="4"/>
+      <c r="AI10" s="3"/>
+      <c r="AJ10" s="7"/>
+      <c r="AK10" s="7"/>
+      <c r="AL10" s="3"/>
       <c r="AM10" s="1"/>
       <c r="AN10" s="1"/>
       <c r="AO10" s="1"/>
@@ -2197,85 +2202,85 @@
       <c r="AW10" s="1"/>
       <c r="AX10" s="1"/>
       <c r="AY10" s="1"/>
-      <c r="AZ10" s="8"/>
+      <c r="AZ10" s="7"/>
       <c r="BA10" s="1"/>
       <c r="BB10" s="1"/>
-      <c r="BC10" s="8"/>
+      <c r="BC10" s="7"/>
       <c r="BD10" s="1"/>
-      <c r="BE10" s="4"/>
-      <c r="BF10" s="4"/>
+      <c r="BE10" s="3"/>
+      <c r="BF10" s="3"/>
       <c r="BG10" s="1"/>
       <c r="BH10" s="1"/>
       <c r="BI10" s="1"/>
       <c r="BJ10" s="1"/>
-      <c r="BK10" s="2"/>
+      <c r="BK10" s="11"/>
       <c r="BL10" s="1"/>
       <c r="BM10" s="1"/>
       <c r="BN10" s="1"/>
       <c r="BO10" s="1"/>
-      <c r="BP10" s="4"/>
-      <c r="BQ10" s="4"/>
+      <c r="BP10" s="3"/>
+      <c r="BQ10" s="3"/>
       <c r="BR10" s="1"/>
       <c r="BS10" s="1"/>
-      <c r="BT10" s="4"/>
+      <c r="BT10" s="3"/>
       <c r="BU10" s="1"/>
       <c r="BV10" s="1"/>
       <c r="BW10" s="1"/>
       <c r="BZ10" s="1"/>
-      <c r="CB10" s="4"/>
-      <c r="CD10" s="2"/>
-      <c r="CE10" s="2"/>
+      <c r="CB10" s="3"/>
+      <c r="CD10" s="11"/>
+      <c r="CE10" s="11"/>
       <c r="CF10" s="1"/>
       <c r="CG10" s="1"/>
-      <c r="CH10" s="3"/>
+      <c r="CH10" s="2"/>
       <c r="CI10" s="1"/>
-      <c r="CJ10" s="8"/>
-      <c r="CK10" s="4"/>
+      <c r="CJ10" s="7"/>
+      <c r="CK10" s="3"/>
       <c r="CL10" s="1"/>
       <c r="CM10" s="1"/>
-      <c r="CO10" s="4"/>
-      <c r="CP10" s="3"/>
+      <c r="CO10" s="3"/>
+      <c r="CP10" s="2"/>
       <c r="CQ10" s="1"/>
     </row>
     <row r="11" spans="1:99">
       <c r="A11" s="1"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="3"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="2"/>
       <c r="D11" s="1"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="1"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="3"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="6"/>
-      <c r="O11" s="8"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="7"/>
       <c r="P11" s="1"/>
-      <c r="Q11" s="8"/>
-      <c r="R11" s="5"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="4"/>
       <c r="S11" s="1"/>
-      <c r="T11" s="8"/>
-      <c r="U11" s="8"/>
-      <c r="V11" s="1"/>
-      <c r="W11" s="3"/>
-      <c r="X11" s="4"/>
-      <c r="Y11" s="1"/>
+      <c r="T11" s="7"/>
+      <c r="U11" s="7"/>
+      <c r="V11" s="7"/>
+      <c r="W11" s="1"/>
+      <c r="X11" s="2"/>
+      <c r="Y11" s="3"/>
       <c r="Z11" s="1"/>
       <c r="AA11" s="1"/>
-      <c r="AB11" s="6"/>
-      <c r="AC11" s="6"/>
+      <c r="AB11" s="1"/>
+      <c r="AC11" s="5"/>
       <c r="AD11" s="1"/>
       <c r="AE11" s="1"/>
       <c r="AF11" s="1"/>
       <c r="AG11" s="1"/>
       <c r="AH11" s="1"/>
-      <c r="AI11" s="4"/>
-      <c r="AJ11" s="8"/>
-      <c r="AK11" s="8"/>
-      <c r="AL11" s="4"/>
+      <c r="AI11" s="3"/>
+      <c r="AJ11" s="7"/>
+      <c r="AK11" s="7"/>
+      <c r="AL11" s="3"/>
       <c r="AM11" s="1"/>
       <c r="AN11" s="1"/>
       <c r="AO11" s="1"/>
@@ -2289,85 +2294,85 @@
       <c r="AW11" s="1"/>
       <c r="AX11" s="1"/>
       <c r="AY11" s="1"/>
-      <c r="AZ11" s="8"/>
+      <c r="AZ11" s="7"/>
       <c r="BA11" s="1"/>
       <c r="BB11" s="1"/>
-      <c r="BC11" s="8"/>
+      <c r="BC11" s="7"/>
       <c r="BD11" s="1"/>
-      <c r="BE11" s="4"/>
-      <c r="BF11" s="4"/>
+      <c r="BE11" s="3"/>
+      <c r="BF11" s="3"/>
       <c r="BG11" s="1"/>
       <c r="BH11" s="1"/>
       <c r="BI11" s="1"/>
       <c r="BJ11" s="1"/>
-      <c r="BK11" s="2"/>
+      <c r="BK11" s="11"/>
       <c r="BL11" s="1"/>
       <c r="BM11" s="1"/>
       <c r="BN11" s="1"/>
       <c r="BO11" s="1"/>
-      <c r="BP11" s="4"/>
-      <c r="BQ11" s="4"/>
+      <c r="BP11" s="3"/>
+      <c r="BQ11" s="3"/>
       <c r="BR11" s="1"/>
       <c r="BS11" s="1"/>
-      <c r="BT11" s="4"/>
+      <c r="BT11" s="3"/>
       <c r="BU11" s="1"/>
       <c r="BV11" s="1"/>
       <c r="BW11" s="1"/>
       <c r="BZ11" s="1"/>
-      <c r="CB11" s="4"/>
-      <c r="CD11" s="2"/>
-      <c r="CE11" s="2"/>
+      <c r="CB11" s="3"/>
+      <c r="CD11" s="11"/>
+      <c r="CE11" s="11"/>
       <c r="CF11" s="1"/>
       <c r="CG11" s="1"/>
-      <c r="CH11" s="3"/>
+      <c r="CH11" s="2"/>
       <c r="CI11" s="1"/>
-      <c r="CJ11" s="8"/>
-      <c r="CK11" s="4"/>
+      <c r="CJ11" s="7"/>
+      <c r="CK11" s="3"/>
       <c r="CL11" s="1"/>
       <c r="CM11" s="1"/>
-      <c r="CO11" s="4"/>
-      <c r="CP11" s="3"/>
+      <c r="CO11" s="3"/>
+      <c r="CP11" s="2"/>
       <c r="CQ11" s="1"/>
     </row>
     <row r="12" spans="1:99">
       <c r="A12" s="1"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="3"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="2"/>
       <c r="D12" s="1"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="1"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="3"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="6"/>
-      <c r="O12" s="8"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="7"/>
       <c r="P12" s="1"/>
-      <c r="Q12" s="8"/>
-      <c r="R12" s="5"/>
+      <c r="Q12" s="7"/>
+      <c r="R12" s="4"/>
       <c r="S12" s="1"/>
-      <c r="T12" s="8"/>
-      <c r="U12" s="8"/>
-      <c r="V12" s="1"/>
-      <c r="W12" s="3"/>
-      <c r="X12" s="4"/>
-      <c r="Y12" s="1"/>
+      <c r="T12" s="7"/>
+      <c r="U12" s="7"/>
+      <c r="V12" s="7"/>
+      <c r="W12" s="1"/>
+      <c r="X12" s="2"/>
+      <c r="Y12" s="3"/>
       <c r="Z12" s="1"/>
       <c r="AA12" s="1"/>
-      <c r="AB12" s="6"/>
-      <c r="AC12" s="6"/>
+      <c r="AB12" s="1"/>
+      <c r="AC12" s="5"/>
       <c r="AD12" s="1"/>
       <c r="AE12" s="1"/>
       <c r="AF12" s="1"/>
       <c r="AG12" s="1"/>
       <c r="AH12" s="1"/>
-      <c r="AI12" s="4"/>
-      <c r="AJ12" s="8"/>
-      <c r="AK12" s="8"/>
-      <c r="AL12" s="4"/>
+      <c r="AI12" s="3"/>
+      <c r="AJ12" s="7"/>
+      <c r="AK12" s="7"/>
+      <c r="AL12" s="3"/>
       <c r="AM12" s="1"/>
       <c r="AN12" s="1"/>
       <c r="AO12" s="1"/>
@@ -2381,85 +2386,85 @@
       <c r="AW12" s="1"/>
       <c r="AX12" s="1"/>
       <c r="AY12" s="1"/>
-      <c r="AZ12" s="8"/>
+      <c r="AZ12" s="7"/>
       <c r="BA12" s="1"/>
       <c r="BB12" s="1"/>
-      <c r="BC12" s="8"/>
+      <c r="BC12" s="7"/>
       <c r="BD12" s="1"/>
-      <c r="BE12" s="4"/>
-      <c r="BF12" s="4"/>
+      <c r="BE12" s="3"/>
+      <c r="BF12" s="3"/>
       <c r="BG12" s="1"/>
       <c r="BH12" s="1"/>
       <c r="BI12" s="1"/>
       <c r="BJ12" s="1"/>
-      <c r="BK12" s="2"/>
+      <c r="BK12" s="11"/>
       <c r="BL12" s="1"/>
       <c r="BM12" s="1"/>
       <c r="BN12" s="1"/>
       <c r="BO12" s="1"/>
-      <c r="BP12" s="4"/>
-      <c r="BQ12" s="4"/>
+      <c r="BP12" s="3"/>
+      <c r="BQ12" s="3"/>
       <c r="BR12" s="1"/>
       <c r="BS12" s="1"/>
-      <c r="BT12" s="4"/>
+      <c r="BT12" s="3"/>
       <c r="BU12" s="1"/>
       <c r="BV12" s="1"/>
       <c r="BW12" s="1"/>
       <c r="BZ12" s="1"/>
-      <c r="CB12" s="4"/>
-      <c r="CD12" s="2"/>
-      <c r="CE12" s="2"/>
+      <c r="CB12" s="3"/>
+      <c r="CD12" s="11"/>
+      <c r="CE12" s="11"/>
       <c r="CF12" s="1"/>
       <c r="CG12" s="1"/>
-      <c r="CH12" s="3"/>
+      <c r="CH12" s="2"/>
       <c r="CI12" s="1"/>
-      <c r="CJ12" s="8"/>
-      <c r="CK12" s="4"/>
+      <c r="CJ12" s="7"/>
+      <c r="CK12" s="3"/>
       <c r="CL12" s="1"/>
       <c r="CM12" s="1"/>
-      <c r="CO12" s="4"/>
-      <c r="CP12" s="3"/>
+      <c r="CO12" s="3"/>
+      <c r="CP12" s="2"/>
       <c r="CQ12" s="1"/>
     </row>
     <row r="13" spans="1:99">
       <c r="A13" s="1"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="3"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="2"/>
       <c r="D13" s="1"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="1"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="3"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="8"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="7"/>
       <c r="P13" s="1"/>
-      <c r="Q13" s="8"/>
-      <c r="R13" s="5"/>
+      <c r="Q13" s="7"/>
+      <c r="R13" s="4"/>
       <c r="S13" s="1"/>
-      <c r="T13" s="8"/>
-      <c r="U13" s="8"/>
-      <c r="V13" s="1"/>
-      <c r="W13" s="3"/>
-      <c r="X13" s="4"/>
-      <c r="Y13" s="1"/>
+      <c r="T13" s="7"/>
+      <c r="U13" s="7"/>
+      <c r="V13" s="7"/>
+      <c r="W13" s="1"/>
+      <c r="X13" s="2"/>
+      <c r="Y13" s="3"/>
       <c r="Z13" s="1"/>
       <c r="AA13" s="1"/>
-      <c r="AB13" s="6"/>
-      <c r="AC13" s="6"/>
+      <c r="AB13" s="1"/>
+      <c r="AC13" s="5"/>
       <c r="AD13" s="1"/>
       <c r="AE13" s="1"/>
       <c r="AF13" s="1"/>
       <c r="AG13" s="1"/>
       <c r="AH13" s="1"/>
-      <c r="AI13" s="4"/>
-      <c r="AJ13" s="8"/>
-      <c r="AK13" s="8"/>
-      <c r="AL13" s="4"/>
+      <c r="AI13" s="3"/>
+      <c r="AJ13" s="7"/>
+      <c r="AK13" s="7"/>
+      <c r="AL13" s="3"/>
       <c r="AM13" s="1"/>
       <c r="AN13" s="1"/>
       <c r="AO13" s="1"/>
@@ -2473,44 +2478,44 @@
       <c r="AW13" s="1"/>
       <c r="AX13" s="1"/>
       <c r="AY13" s="1"/>
-      <c r="AZ13" s="8"/>
+      <c r="AZ13" s="7"/>
       <c r="BA13" s="1"/>
       <c r="BB13" s="1"/>
-      <c r="BC13" s="8"/>
+      <c r="BC13" s="7"/>
       <c r="BD13" s="1"/>
-      <c r="BE13" s="4"/>
-      <c r="BF13" s="4"/>
+      <c r="BE13" s="3"/>
+      <c r="BF13" s="3"/>
       <c r="BG13" s="1"/>
       <c r="BH13" s="1"/>
       <c r="BI13" s="1"/>
       <c r="BJ13" s="1"/>
-      <c r="BK13" s="2"/>
+      <c r="BK13" s="11"/>
       <c r="BL13" s="1"/>
       <c r="BM13" s="1"/>
       <c r="BN13" s="1"/>
       <c r="BO13" s="1"/>
-      <c r="BP13" s="4"/>
-      <c r="BQ13" s="4"/>
+      <c r="BP13" s="3"/>
+      <c r="BQ13" s="3"/>
       <c r="BR13" s="1"/>
       <c r="BS13" s="1"/>
-      <c r="BT13" s="4"/>
+      <c r="BT13" s="3"/>
       <c r="BU13" s="1"/>
       <c r="BV13" s="1"/>
       <c r="BW13" s="1"/>
       <c r="BZ13" s="1"/>
-      <c r="CB13" s="4"/>
-      <c r="CD13" s="2"/>
-      <c r="CE13" s="2"/>
+      <c r="CB13" s="3"/>
+      <c r="CD13" s="11"/>
+      <c r="CE13" s="11"/>
       <c r="CF13" s="1"/>
       <c r="CG13" s="1"/>
-      <c r="CH13" s="3"/>
+      <c r="CH13" s="2"/>
       <c r="CI13" s="1"/>
-      <c r="CJ13" s="8"/>
-      <c r="CK13" s="4"/>
+      <c r="CJ13" s="7"/>
+      <c r="CK13" s="3"/>
       <c r="CL13" s="1"/>
       <c r="CM13" s="1"/>
-      <c r="CO13" s="4"/>
-      <c r="CP13" s="3"/>
+      <c r="CO13" s="3"/>
+      <c r="CP13" s="2"/>
       <c r="CQ13" s="1"/>
     </row>
   </sheetData>
